--- a/tools/importer/reports/import-news-article-v1.report.xlsx
+++ b/tools/importer/reports/import-news-article-v1.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="641">
   <si>
     <t>_reportFile</t>
   </si>
@@ -82,6 +82,21 @@
     <t>http://localhost:3000/content/nav.plain.html</t>
   </si>
   <si>
+    <t>en/home.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-media","columns-media","cards-pricing","cards-media","cards-media","cards-media","columns-cta","columns-quote","columns-quote","accordion","form"]</t>
+  </si>
+  <si>
+    <t>en/home</t>
+  </si>
+  <si>
+    <t>2026-10-19T06:52:56.826Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home.html</t>
+  </si>
+  <si>
     <t>es/nav.report.json</t>
   </si>
   <si>
@@ -94,21 +109,129 @@
     <t>http://localhost:3000/content/es/nav.plain.html</t>
   </si>
   <si>
+    <t>drafts/block-samples/columns-article-embed.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-article-embed</t>
+  </si>
+  <si>
+    <t>block-sample</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:41:45.115Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/jack-and-jill-usta-coaching-tennis-for-black-families.html</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-grid-mobile.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-grid-mobile</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:41:17.315Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/sportimes-playbook-for-the-modern-tennis-coach.html</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-grid-tablet.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-grid-tablet</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:41:06.918Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/how-usta-coaching-benefits-college-tennis-coaches.html</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-grid.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/columns-grid</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:40:53.199Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/advantage-coaches-celebrating-one-year-of-usta-coaching.html</t>
+  </si>
+  <si>
     <t>drafts/block-samples/columns-person.report.json</t>
   </si>
   <si>
     <t>drafts/block-samples/columns-person</t>
   </si>
   <si>
-    <t>block-sample</t>
-  </si>
-  <si>
-    <t>2026-10-07T11:09:28.426Z</t>
+    <t>2026-10-07T18:56:57.466Z</t>
   </si>
   <si>
     <t>https://www.ustacoaching.com/en/home/news/coaches-reveal-their-game-changing-goals-for-2026.html</t>
   </si>
   <si>
+    <t>drafts/block-samples/quote-marks.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/quote-marks</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:43:42.423Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/how-coach-developer-lois-arterberry-is-shaping-the-future-of-coaching.html</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-center.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-center</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:42:21.043Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/how-usta-coaching-benefits-college-tennis-coaches.html#center</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-intro.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-intro</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:43:32.814Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/women-in-coaching-advancing-female-tennis-coach-development.html</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-label.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-label</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:42:05.492Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/usta-coaching-wecoach.html</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-large.report.json</t>
+  </si>
+  <si>
+    <t>drafts/block-samples/text-style-large</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:43:22.140Z</t>
+  </si>
+  <si>
+    <t>https://www.ustacoaching.com/en/home/news/usta-coaching-online-learning-hub-is-live.html</t>
+  </si>
+  <si>
     <t>fragments/news/featured-article.report.json</t>
   </si>
   <si>
@@ -133,7 +256,7 @@
     <t>news-article</t>
   </si>
   <si>
-    <t>2026-10-07T12:43:44.980Z</t>
+    <t>2026-10-08T00:00:55.920Z</t>
   </si>
   <si>
     <t>High School Tennis Coaching: 10 Tips for Coaches &amp; Parents | USTA Coaching</t>
@@ -148,22 +271,19 @@
     <t>en/home/news/advantage-coaches-celebrating-one-year-of-usta-coaching</t>
   </si>
   <si>
-    <t>2026-10-07T12:43:51.825Z</t>
+    <t>2026-10-08T00:01:03.982Z</t>
   </si>
   <si>
     <t>Advantage, Coaches – Celebrating One Year of USTA Coaching</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/advantage-coaches-celebrating-one-year-of-usta-coaching.html</t>
-  </si>
-  <si>
     <t>en/home/news/black-girls-tennis-club-redefining-who-belongs-on-court.report.json</t>
   </si>
   <si>
     <t>en/home/news/black-girls-tennis-club-redefining-who-belongs-on-court</t>
   </si>
   <si>
-    <t>2026-10-07T12:43:59.097Z</t>
+    <t>2026-10-08T00:01:11.168Z</t>
   </si>
   <si>
     <t>Black Girls Tennis Club Is Redefining Who Belongs on the Court</t>
@@ -178,7 +298,7 @@
     <t>en/home/news/cardio-tennis-makes-business-sense-for-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:44:05.020Z</t>
+    <t>2026-10-08T00:01:17.748Z</t>
   </si>
   <si>
     <t>Why Cardio Tennis Makes Business Sense for Tennis Coaches</t>
@@ -193,7 +313,7 @@
     <t>en/home/news/coach-guide-to-tennis-hydration</t>
   </si>
   <si>
-    <t>2026-10-07T12:44:12.019Z</t>
+    <t>2026-10-08T00:01:23.905Z</t>
   </si>
   <si>
     <t>Hydration Tips for Tennis Players: A Coach’s Guide | USTA Coaching</t>
@@ -208,7 +328,7 @@
     <t>en/home/news/coaches-open-2026</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:04.677Z</t>
+    <t>2026-10-08T00:02:17.419Z</t>
   </si>
   <si>
     <t>Inaugural Coaches Open Energizes Tennis Coaching Community</t>
@@ -223,7 +343,7 @@
     <t>en/home/news/coaches-reveal-their-game-changing-goals-for-2026</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:10.877Z</t>
+    <t>2026-10-08T00:02:24.617Z</t>
   </si>
   <si>
     <t>Net Gains – Coaches Reveal Their Game-Changing Goals for 2026</t>
@@ -235,7 +355,7 @@
     <t>en/home/news/coaching-promising-junior-tennis-players-troy-hahn</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:17.537Z</t>
+    <t>2026-10-08T00:02:31.011Z</t>
   </si>
   <si>
     <t>Coaching Promising Junior Tennis Players: Troy Hahn on Parents, Process and Long-Term Development</t>
@@ -250,7 +370,7 @@
     <t>en/home/news/coachs-journal-emma-dell-first-impressions</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:23.631Z</t>
+    <t>2026-10-08T00:02:37.179Z</t>
   </si>
   <si>
     <t>Coach’s Journal by Emma Dell – Part 1: First Impressions | USTA Coaching</t>
@@ -265,7 +385,7 @@
     <t>en/home/news/coachs-journal-emma-dell-part-2-serve-your-passion</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:30.378Z</t>
+    <t>2026-10-08T00:02:43.168Z</t>
   </si>
   <si>
     <t>Coach’s Journal by Emma Dell – Part 2: What Does It Mean to Serve Your Passion?</t>
@@ -280,7 +400,7 @@
     <t>en/home/news/coachs-journal-emma-dell-part-3-changing-sides-net</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:38.450Z</t>
+    <t>2026-10-08T00:02:50.394Z</t>
   </si>
   <si>
     <t>Coach’s Journal by Emma Dell – Part 3: Changing Sides of the Net</t>
@@ -295,7 +415,7 @@
     <t>en/home/news/dr-larry-lauer-on-mental-health-and-performance-in-tennis</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:44.387Z</t>
+    <t>2026-10-08T00:02:56.775Z</t>
   </si>
   <si>
     <t>Coaching the Whole Player: Dr. Larry Lauer on Mental Health and Performance in Tennis</t>
@@ -310,7 +430,7 @@
     <t>en/home/news/emilio-sanchez-academy-building-coaches-and-players-through-spanish-system</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:51.878Z</t>
+    <t>2026-10-08T00:03:02.711Z</t>
   </si>
   <si>
     <t>Emilio Sánchez Academy: Building Coaches and Players Through a Proven Spanish System</t>
@@ -325,7 +445,7 @@
     <t>en/home/news/from-qualifier-to-champion-tina-lee-jordan-wimbledon-triumph</t>
   </si>
   <si>
-    <t>2026-10-07T12:45:57.577Z</t>
+    <t>2026-10-08T00:03:08.835Z</t>
   </si>
   <si>
     <t>From Qualifier to Champion – Tina Lee on the Grit Behind Jordan’s Wimbledon Triumph</t>
@@ -340,7 +460,7 @@
     <t>en/home/news/ghanaian-coachs-journey-through-coach-inclusion-summit</t>
   </si>
   <si>
-    <t>2026-10-07T12:46:04.665Z</t>
+    <t>2026-10-08T00:03:14.564Z</t>
   </si>
   <si>
     <t>From Ball Boy to Change Maker: A Ghanaian Coach’s Journey Through the Coach Inclusion Summit</t>
@@ -355,7 +475,7 @@
     <t>en/home/news/gordon-reid-making-tennis-welcoming</t>
   </si>
   <si>
-    <t>2026-10-07T12:46:11.263Z</t>
+    <t>2026-10-08T00:03:19.813Z</t>
   </si>
   <si>
     <t>Gordon Reid on Making Tennis Welcoming for All and Future-Proofing Your Career</t>
@@ -370,7 +490,7 @@
     <t>en/home/news/growth-and-success-of-wta-female-coaching-initiatives</t>
   </si>
   <si>
-    <t>2026-10-07T12:46:46.462Z</t>
+    <t>2026-10-08T00:03:26.080Z</t>
   </si>
   <si>
     <t>Building Pathways: The Growth and Success of WTA Female Coaching Initiatives</t>
@@ -385,7 +505,7 @@
     <t>en/home/news/how-blind-tennis-builds-confidence-independence</t>
   </si>
   <si>
-    <t>2026-10-07T12:46:52.613Z</t>
+    <t>2026-10-08T00:03:32.465Z</t>
   </si>
   <si>
     <t>How Blind Tennis Builds Confidence &amp; Independence | USTA Coaching</t>
@@ -400,22 +520,19 @@
     <t>en/home/news/how-coach-developer-lois-arterberry-is-shaping-the-future-of-coaching</t>
   </si>
   <si>
-    <t>2026-10-07T12:46:59.874Z</t>
+    <t>2026-10-08T00:03:37.991Z</t>
   </si>
   <si>
     <t>From D1 Head Coach to Student: Why Lois Arterberry Chose the Coach Developer Pathway</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/how-coach-developer-lois-arterberry-is-shaping-the-future-of-coaching.html</t>
-  </si>
-  <si>
     <t>en/home/news/how-dana-matthewson-relearned-the-game-as-a-coach.report.json</t>
   </si>
   <si>
     <t>en/home/news/how-dana-matthewson-relearned-the-game-as-a-coach</t>
   </si>
   <si>
-    <t>2026-10-07T12:47:05.621Z</t>
+    <t>2026-10-08T00:03:45.035Z</t>
   </si>
   <si>
     <t>From Tour to Teaching: How Dana Mathewson Relearned the Game as a Coach</t>
@@ -430,7 +547,7 @@
     <t>en/home/news/how-one-coach-helped-change-community-through-usta-coaching-education</t>
   </si>
   <si>
-    <t>2026-10-07T12:47:11.163Z</t>
+    <t>2026-10-08T00:03:52.253Z</t>
   </si>
   <si>
     <t>How One Coach Helped Change a Community Through USTA Coaching Education</t>
@@ -445,22 +562,19 @@
     <t>en/home/news/how-usta-coaching-benefits-college-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:47:17.668Z</t>
+    <t>2026-10-08T00:03:58.580Z</t>
   </si>
   <si>
     <t>How USTA Coaching Benefits College Tennis Coaches</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/how-usta-coaching-benefits-college-tennis-coaches.html</t>
-  </si>
-  <si>
     <t>en/home/news/how-usta-coaching-helps-parks-recreation-coaches.report.json</t>
   </si>
   <si>
     <t>en/home/news/how-usta-coaching-helps-parks-recreation-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:47:24.727Z</t>
+    <t>2026-10-08T00:04:06.324Z</t>
   </si>
   <si>
     <t>Why USTA Coaching Is a Winning Play for Park &amp; Recreation</t>
@@ -475,7 +589,7 @@
     <t>en/home/news/inside-the-coach-inclusion-summit-powered-by-usta-coaching</t>
   </si>
   <si>
-    <t>2026-10-07T12:47:30.176Z</t>
+    <t>2026-10-08T00:04:14.090Z</t>
   </si>
   <si>
     <t>Empowering Every Player: Inside the Coach Inclusion Summit powered by USTA Coaching</t>
@@ -490,7 +604,7 @@
     <t>en/home/news/inspiring-story-of-brittany-odom-dennis-quaye</t>
   </si>
   <si>
-    <t>2026-10-07T12:47:35.767Z</t>
+    <t>2026-10-08T00:04:21.464Z</t>
   </si>
   <si>
     <t>Serving Love: The Inspiring Story of Brittany Odom &amp; Dennis Quaye</t>
@@ -505,22 +619,19 @@
     <t>en/home/news/jack-and-jill-usta-coaching-tennis-for-black-families</t>
   </si>
   <si>
-    <t>2026-10-07T12:48:28.402Z</t>
+    <t>2026-10-08T00:05:14.453Z</t>
   </si>
   <si>
     <t>Jack and Jill &amp; USTA Coaching: Tennis for Black Families</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/jack-and-jill-usta-coaching-tennis-for-black-families.html</t>
-  </si>
-  <si>
     <t>en/home/news/janet-pinkett-building-opportunity-and-joy-in-youth-tennis-thro.report.json</t>
   </si>
   <si>
     <t>en/home/news/janet-pinkett-building-opportunity-and-joy-in-youth-tennis-thro</t>
   </si>
   <si>
-    <t>2026-10-07T12:48:35.478Z</t>
+    <t>2026-10-08T00:05:22.324Z</t>
   </si>
   <si>
     <t>Janet Pinkett: Building Opportunity and Joy in Youth Tennis Through USTA Mid-Atlantic Foundation’s Girls Rule the Court™</t>
@@ -535,7 +646,7 @@
     <t>en/home/news/jim-loehr-lasting-lessons-for-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:48:41.759Z</t>
+    <t>2026-10-08T00:05:29.890Z</t>
   </si>
   <si>
     <t>Jim Loehr’s Lasting Lessons for Tennis Coaches</t>
@@ -550,7 +661,7 @@
     <t>en/home/news/john-wilkersons-50-year-coaching-legacy</t>
   </si>
   <si>
-    <t>2026-10-07T12:48:47.931Z</t>
+    <t>2026-10-08T00:05:36.763Z</t>
   </si>
   <si>
     <t>John Wilkerson’s 50-Year Coaching Legacy: Lessons in Belief, Community and Opportunity</t>
@@ -565,7 +676,7 @@
     <t>en/home/news/junior-usa-tennis-shows-true-sportsmanship-at-world-team-cup</t>
   </si>
   <si>
-    <t>2026-10-07T12:48:53.247Z</t>
+    <t>2026-10-08T00:05:43.623Z</t>
   </si>
   <si>
     <t>Junior USA Team Shows True Sportsmanship at World Team Cup</t>
@@ -580,7 +691,7 @@
     <t>en/home/news/love-serving-autism-coaches-lead-with-acceptance-on-tennis-court</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:00.874Z</t>
+    <t>2026-10-08T00:05:49.474Z</t>
   </si>
   <si>
     <t>Love Serving Autism: How Coaches Can Lead with Acceptance on the Tennis Court</t>
@@ -595,7 +706,7 @@
     <t>en/home/news/make-tennis-more-welcoming-for-everybody</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:07.613Z</t>
+    <t>2026-10-08T00:05:55.237Z</t>
   </si>
   <si>
     <t>How Coaches Can Make Tennis More Welcoming for Everybody</t>
@@ -610,7 +721,7 @@
     <t>en/home/news/michael-harpers-advice-for-tennis-parents-and-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:15.177Z</t>
+    <t>2026-10-08T00:06:01.294Z</t>
   </si>
   <si>
     <t>Michael Harper’s Advice for Tennis Parents and Coaches: Play the Long Game</t>
@@ -625,7 +736,7 @@
     <t>en/home/news/new-usta-coaching-upgrades</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:22.316Z</t>
+    <t>2026-10-08T00:06:35.970Z</t>
   </si>
   <si>
     <t>New Education Badges, USTA Coaching App &amp; More</t>
@@ -640,7 +751,7 @@
     <t>en/home/news/paul-annacone-2026-us-open-american-stars-to-watch</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:30.506Z</t>
+    <t>2026-10-08T00:06:42.375Z</t>
   </si>
   <si>
     <t>Paul Annacone 2026 US Open Preview: American Stars to Watch</t>
@@ -655,7 +766,7 @@
     <t>en/home/news/practical-strategies-and-tips-for-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:37.621Z</t>
+    <t>2026-10-08T00:06:48.629Z</t>
   </si>
   <si>
     <t>Coaching the Mental Game: Practical Strategies &amp; Tips for Tennis Coaches</t>
@@ -693,7 +804,7 @@
     <t>en/home/news/serving-gratitude-celebrating-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:44.275Z</t>
+    <t>2026-10-08T00:06:56.500Z</t>
   </si>
   <si>
     <t>Serving Gratitude: Celebrating Tennis Coaches | USTA Coaching</t>
@@ -705,7 +816,7 @@
     <t>en/home/news/southlake-tennis-center-coaching-excellence-world-class-facilities</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:50.099Z</t>
+    <t>2026-10-08T00:07:03.414Z</t>
   </si>
   <si>
     <t>Southlake Tennis Center Builds Coaching Excellence Through World-Class Facilities</t>
@@ -714,28 +825,46 @@
     <t>https://www.ustacoaching.com/en/home/news/southlake-tennis-center-coaching-excellence-world-class-facilities.html</t>
   </si>
   <si>
+    <t>en/home/news/sportimes-playbook-for-the-modern-tennis-coach.html.report.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.evaluate: Error: Failed to import page: no /^Columns \(grid, mobile\)$/ block in sportimes-playbook-for-the-modern-tennis-coach: Columns (article, Media Right, Media 3, flush) | Quote | Spacer | Columns (article, Media Right, Media 5) | Columns (article, Media Left, Media 6) | Columns (article, Media Right, Media 4) | Columns (grid, Mobile) | Tags | Social | Section Metadata | Fragment | Metadata
+    at eval (eval at evaluate (:290:30), &lt;anonymous&gt;:29:15)
+    at async &lt;anonymous&gt;:316:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.evaluate: Error: Failed to import page: no /^Columns \(grid, mobile\)$/ block in sportimes-playbook-for-the-modern-tennis-coach: Columns (article, Media Right, Media 3, flush) | Quote | Spacer | Columns (article, Media Right, Media 5) | Columns (article, Media Left, Media 6) | Columns (article, Media Right, Media 4) | Columns (grid, Mobile) | Tags | Social | Section Metadata | Fragment | Metadata
+    at eval (eval at evaluate (:290:30), &lt;anonymous&gt;:29:15)
+    at async &lt;anonymous&gt;:316:30
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:693:31)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:956:22)</t>
+  </si>
+  <si>
+    <t>en/home/news/sportimes-playbook-for-the-modern-tennis-coach.html</t>
+  </si>
+  <si>
+    <t>2026-10-07T20:26:44.494Z</t>
+  </si>
+  <si>
     <t>en/home/news/sportimes-playbook-for-the-modern-tennis-coach.report.json</t>
   </si>
   <si>
     <t>en/home/news/sportimes-playbook-for-the-modern-tennis-coach</t>
   </si>
   <si>
-    <t>2026-10-07T12:49:57.750Z</t>
+    <t>2026-10-08T00:07:09.984Z</t>
   </si>
   <si>
     <t>Sportime’s Playbook for the Modern Coach</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/sportimes-playbook-for-the-modern-tennis-coach.html</t>
-  </si>
-  <si>
     <t>en/home/news/sportsmen-tennis-enrichment-center-njtl-leader-boston.report.json</t>
   </si>
   <si>
     <t>en/home/news/sportsmen-tennis-enrichment-center-njtl-leader-boston</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:04.662Z</t>
+    <t>2026-10-08T00:07:17.279Z</t>
   </si>
   <si>
     <t>Sportsmen’s Tennis &amp; Enrichment Center: A Mission-Driven NJTL Leader in Boston</t>
@@ -750,7 +879,7 @@
     <t>en/home/news/thomas-judd-coaching-across-continents-ncaa-recruiting-and-business-of-tennis</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:10.456Z</t>
+    <t>2026-10-08T00:07:22.751Z</t>
   </si>
   <si>
     <t>Thomas Judd on Coaching Across Continents, NCAA Recruiting and the Business of Tennis</t>
@@ -765,7 +894,7 @@
     <t>en/home/news/usta-ceo-craig-tileys-vision-for-american-tennis</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:17.164Z</t>
+    <t>2026-10-08T00:07:29.954Z</t>
   </si>
   <si>
     <t>Incoming USTA CEO Craig Tiley’s Vision for American Tennis | USTA Coaching</t>
@@ -780,7 +909,7 @@
     <t>en/home/news/usta-coaching-butch-staples-award-2026-coaches-open</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:23.570Z</t>
+    <t>2026-10-08T00:07:36.977Z</t>
   </si>
   <si>
     <t>USTA Coaching Butch Staples Award Presented at 2026 Coaches Open</t>
@@ -795,7 +924,7 @@
     <t>en/home/news/usta-coaching-collaborates-with-ptm-programs-to-develop-next-generation-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:29.539Z</t>
+    <t>2026-10-08T00:07:43.457Z</t>
   </si>
   <si>
     <t>USTA Coaching Collaborates with PTM Programs to Develop Next-Generation Tennis Coaches</t>
@@ -810,7 +939,7 @@
     <t>en/home/news/usta-coaching-gives-tennis-coaches-tips-how-to-create-2026-vision-board</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:34.939Z</t>
+    <t>2026-10-08T00:07:51.384Z</t>
   </si>
   <si>
     <t>USTA Coaching Gives Tennis Coaches Tips on How to Create Their 2026 Vision Board</t>
@@ -825,7 +954,7 @@
     <t>en/home/news/usta-coaching-launches-inaugural-women-coaching-cohort</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:41.079Z</t>
+    <t>2026-10-08T00:07:57.958Z</t>
   </si>
   <si>
     <t>USTA Coaching Launches Inaugural Women in Coaching Cohort to Elevate Leadership</t>
@@ -840,22 +969,19 @@
     <t>en/home/news/usta-coaching-online-learning-hub-is-live</t>
   </si>
   <si>
-    <t>2026-10-07T12:51:34.606Z</t>
+    <t>2026-10-19T08:49:57.006Z</t>
   </si>
   <si>
     <t>USTA Coaching Online Learning Hub Is Live!</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/usta-coaching-online-learning-hub-is-live.html</t>
-  </si>
-  <si>
     <t>en/home/news/usta-coaching-testimonials-7-coaches-share-their-experience.report.json</t>
   </si>
   <si>
     <t>en/home/news/usta-coaching-testimonials-7-coaches-share-their-experience</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:10.695Z</t>
+    <t>2026-10-08T00:09:26.628Z</t>
   </si>
   <si>
     <t>USTA Coaching Testimonials: 7 Top Coaches Share Their Experience</t>
@@ -870,22 +996,19 @@
     <t>en/home/news/usta-coaching-wecoach</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:18.246Z</t>
+    <t>2026-10-08T00:09:32.602Z</t>
   </si>
   <si>
     <t>Explore a Future in Tennis Coaching with USTA Coaching Serving All: Aspiring Coaches powered by WeCOACH</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/usta-coaching-wecoach.html</t>
-  </si>
-  <si>
     <t>en/home/news/usta-dinkins-hbcu-coaching-grant-helped-2-student-athletes-become-coaches.report.json</t>
   </si>
   <si>
     <t>en/home/news/usta-dinkins-hbcu-coaching-grant-helped-2-student-athletes-become-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:25.999Z</t>
+    <t>2026-10-08T00:09:38.909Z</t>
   </si>
   <si>
     <t>How the USTA Dinkins HBCU Coaching Grant Helped Two Student-Athletes Become Coaches</t>
@@ -900,7 +1023,7 @@
     <t>en/home/news/usta-school-tennis-programs-guide-for-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:33.175Z</t>
+    <t>2026-10-08T00:09:45.985Z</t>
   </si>
   <si>
     <t>USTA School Tennis Programs: A Guide for Coaches | USTA Coaching</t>
@@ -915,7 +1038,7 @@
     <t>en/home/news/vania-king-inclusion-culture-pathway-pro</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:39.276Z</t>
+    <t>2026-10-08T00:09:52.086Z</t>
   </si>
   <si>
     <t>Vania King: What Tennis Coaches Can Learn About Inclusion, Culture and the Pathway to Pro</t>
@@ -930,7 +1053,7 @@
     <t>en/home/news/women-coaches-french-open-immersion-experience</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:47.284Z</t>
+    <t>2026-10-08T00:10:26.570Z</t>
   </si>
   <si>
     <t>Women Coaches Build Skills &amp; Confidence at French Open Immersion Experience</t>
@@ -945,7 +1068,7 @@
     <t>en/home/news/women-coaches-on-the-mentors-who-shaped-them</t>
   </si>
   <si>
-    <t>2026-10-07T12:52:54.526Z</t>
+    <t>2026-10-08T00:10:34.420Z</t>
   </si>
   <si>
     <t>11 Women Coaches on the Mentors Who Shaped Them &amp; Advice for the Next Generation</t>
@@ -960,22 +1083,19 @@
     <t>en/home/news/women-in-coaching-advancing-female-tennis-coach-development</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:00.403Z</t>
+    <t>2026-10-08T00:10:40.855Z</t>
   </si>
   <si>
     <t>Women in Coaching: Advancing Female Tennis Coach Development</t>
   </si>
   <si>
-    <t>https://www.ustacoaching.com/en/home/news/women-in-coaching-advancing-female-tennis-coach-development.html</t>
-  </si>
-  <si>
     <t>en/home/news/zina-garrison-star-player-to-community-builder.report.json</t>
   </si>
   <si>
     <t>en/home/news/zina-garrison-star-player-to-community-builder</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:06.203Z</t>
+    <t>2026-10-08T00:10:48.089Z</t>
   </si>
   <si>
     <t>Zina Garrison: From Star Player to Community Builder</t>
@@ -990,7 +1110,7 @@
     <t>es/home/news/10-tennis-coaching-tips-for-coaches-and-parents</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:14.351Z</t>
+    <t>2026-10-08T00:11:23.452Z</t>
   </si>
   <si>
     <t>Entrenamiento de tenis en la escuela secundaria: 10 Consejos para entrenadores y padres | Entrenamiento de la USTA</t>
@@ -1005,7 +1125,7 @@
     <t>es/home/news/advantage-coaches-celebrating-one-year-of-usta-coaching</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:21.393Z</t>
+    <t>2026-10-08T00:11:29.963Z</t>
   </si>
   <si>
     <t>Advantage, entrenadores: celebrando un año de entrenamiento en la USTA</t>
@@ -1020,7 +1140,7 @@
     <t>es/home/news/black-girls-tennis-club-redefining-who-belongs-on-court</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:30.121Z</t>
+    <t>2026-10-08T00:11:37.730Z</t>
   </si>
   <si>
     <t>El Black Girls Tennis Club está redefiniendo quién pertenece a la cancha</t>
@@ -1035,7 +1155,7 @@
     <t>es/home/news/cardio-tennis-makes-business-sense-for-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:36.757Z</t>
+    <t>2026-10-08T00:11:44.379Z</t>
   </si>
   <si>
     <t>¿Por qué el Cardio Tennis tiene sentido comercial para los entrenadores de tenis?</t>
@@ -1050,7 +1170,7 @@
     <t>es/home/news/coach-guide-to-tennis-hydration</t>
   </si>
   <si>
-    <t>2026-10-07T12:53:43.835Z</t>
+    <t>2026-10-08T00:11:50.712Z</t>
   </si>
   <si>
     <t>Consejos de hidratación para tenistas: Guía para entrenadores | USTA Coaching</t>
@@ -1065,7 +1185,7 @@
     <t>es/home/news/coaches-open-2026</t>
   </si>
   <si>
-    <t>2026-10-07T12:54:36.883Z</t>
+    <t>2026-10-08T00:12:45.137Z</t>
   </si>
   <si>
     <t>La inauguración de la primera edición de la conferencia de entrenadores dinamiza la comunidad de entrenadores de tenis.</t>
@@ -1080,7 +1200,7 @@
     <t>es/home/news/coaches-reveal-their-game-changing-goals-for-2026</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:12.975Z</t>
+    <t>2026-10-08T00:12:53.370Z</t>
   </si>
   <si>
     <t>Ganancias netas: Los entrenadores revelan sus objetivos revolucionarios para 2026</t>
@@ -1095,7 +1215,7 @@
     <t>es/home/news/coaching-promising-junior-tennis-players-troy-hahn</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:18.702Z</t>
+    <t>2026-10-08T00:12:59.061Z</t>
   </si>
   <si>
     <t>Entrenamiento de jóvenes tenistas prometedores: Troy Hahn habla sobre los padres, el proceso y el desarrollo a largo plazo.</t>
@@ -1110,7 +1230,7 @@
     <t>es/home/news/coachs-journal-emma-dell-first-impressions</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:26.277Z</t>
+    <t>2026-10-08T00:13:34.446Z</t>
   </si>
   <si>
     <t>Diario de la entrenadora por Emma Dell – Parte 1: Primeras impresiones | Entrenamiento USTA</t>
@@ -1125,7 +1245,7 @@
     <t>es/home/news/coachs-journal-emma-dell-part-2-serve-your-passion</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:33.061Z</t>
+    <t>2026-10-08T00:14:09.387Z</t>
   </si>
   <si>
     <t>Diario de una entrenadora por Emma Dell – Parte 2: ¿Qué significa servir a tu pasión?</t>
@@ -1140,7 +1260,7 @@
     <t>es/home/news/coachs-journal-emma-dell-part-3-changing-sides-net</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:38.958Z</t>
+    <t>2026-10-08T00:14:43.328Z</t>
   </si>
   <si>
     <t>Diario de la entrenadora por Emma Dell – Parte 3: Cambiando de lado de la red</t>
@@ -1155,7 +1275,7 @@
     <t>es/home/news/dr-larry-lauer-on-mental-health-and-performance-in-tennis</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:45.691Z</t>
+    <t>2026-10-08T00:15:18.532Z</t>
   </si>
   <si>
     <t>Capacitando al jugador integral: El Dr. Larry Lauer sobre la salud mental y el rendimiento en el tenis.</t>
@@ -1170,7 +1290,7 @@
     <t>es/home/news/emilio-sanchez-academy-building-coaches-and-players-through-spanish-system</t>
   </si>
   <si>
-    <t>2026-10-07T12:55:53.069Z</t>
+    <t>2026-10-08T00:15:26.030Z</t>
   </si>
   <si>
     <t>Academia Emilio Sánchez: Formando entrenadores y jugadores a través de un sistema español probado.</t>
@@ -1185,7 +1305,7 @@
     <t>es/home/news/from-qualifier-to-champion-tina-lee-jordan-wimbledon-triumph</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:00.253Z</t>
+    <t>2026-10-08T00:15:33.625Z</t>
   </si>
   <si>
     <t>De jugadora de la fase previa a campeona: Tina Lee habla sobre la garra que impulsó el triunfo de Jordan en Wimbledon.</t>
@@ -1200,7 +1320,7 @@
     <t>es/home/news/ghanaian-coachs-journey-through-coach-inclusion-summit</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:07.512Z</t>
+    <t>2026-10-08T00:15:42.295Z</t>
   </si>
   <si>
     <t>De recogepelotas a creador de cambios: la trayectoria de un entrenador ghanés en la Cumbre de Inclusión de Entrenadores</t>
@@ -1215,7 +1335,7 @@
     <t>es/home/news/gordon-reid-making-tennis-welcoming</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:13.827Z</t>
+    <t>2026-10-08T00:15:48.319Z</t>
   </si>
   <si>
     <t>Gordon Reid habla sobre cómo hacer que el tenis sea accesible para todos y cómo cerciorar el futuro de tu carrera.</t>
@@ -1230,7 +1350,7 @@
     <t>es/home/news/growth-and-success-of-wta-female-coaching-initiatives</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:19.407Z</t>
+    <t>2026-10-08T00:15:55.533Z</t>
   </si>
   <si>
     <t>Construyendo Caminos: El Crecimiento y el Éxito de las Iniciativas de Entrenamiento Femenino de la WTA</t>
@@ -1245,7 +1365,7 @@
     <t>es/home/news/how-blind-tennis-builds-confidence-independence</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:26.521Z</t>
+    <t>2026-10-08T00:16:02.421Z</t>
   </si>
   <si>
     <t>Cómo el tenis para personas ciegas fomenta la confianza y la independencia | Entrenamiento de la USTA</t>
@@ -1260,7 +1380,7 @@
     <t>es/home/news/how-coach-developer-lois-arterberry-is-shaping-the-future-of-coaching</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:33.753Z</t>
+    <t>2026-10-08T00:16:08.825Z</t>
   </si>
   <si>
     <t>De Coach1 a Estudiante: Por qué Lois Arterberry eligió el camino de Coach Desarrolladora</t>
@@ -1275,7 +1395,7 @@
     <t>es/home/news/how-dana-matthewson-relearned-the-game-as-a-coach</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:40.659Z</t>
+    <t>2026-10-08T00:16:15.637Z</t>
   </si>
   <si>
     <t>De la voltea a la docencia: cómo Dana Mathewson volvió a aprender el juego como entrenador</t>
@@ -1290,7 +1410,7 @@
     <t>es/home/news/how-one-coach-helped-change-community-through-usta-coaching-education</t>
   </si>
   <si>
-    <t>2026-10-07T12:56:48.487Z</t>
+    <t>2026-10-08T00:16:23.154Z</t>
   </si>
   <si>
     <t>Cómo un entrenador ayudó a transformar una comunidad a través de la formación de entrenadores de la USTA.</t>
@@ -1305,7 +1425,7 @@
     <t>es/home/news/how-usta-coaching-benefits-college-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:57:23.604Z</t>
+    <t>2026-10-08T00:16:58.022Z</t>
   </si>
   <si>
     <t>Cómo beneficia el entrenamiento de la USTA a los entrenadores de tenis universitarios</t>
@@ -1320,7 +1440,7 @@
     <t>es/home/news/how-usta-coaching-helps-parks-recreation-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:57:31.459Z</t>
+    <t>2026-10-08T00:17:04.966Z</t>
   </si>
   <si>
     <t>Por qué el entrenamiento de la USTA es una apuesta ganadora para parques y recreación.</t>
@@ -1335,7 +1455,7 @@
     <t>es/home/news/inside-the-coach-inclusion-summit-powered-by-usta-coaching</t>
   </si>
   <si>
-    <t>2026-10-07T12:57:37.750Z</t>
+    <t>2026-10-08T00:17:11.647Z</t>
   </si>
   <si>
     <t>Empoderando a cada jugador: Dentro de la Cumbre de Inclusión de Entrenadores impulsada por USTA Coaching</t>
@@ -1350,7 +1470,7 @@
     <t>es/home/news/inspiring-story-of-brittany-odom-dennis-quaye</t>
   </si>
   <si>
-    <t>2026-10-07T12:57:46.027Z</t>
+    <t>2026-10-08T00:17:17.939Z</t>
   </si>
   <si>
     <t>Sirviendo el amor: La inspiradora historia de Brittany Odom y Dennis Quaye</t>
@@ -1365,7 +1485,7 @@
     <t>es/home/news/jack-and-jill-usta-coaching-tennis-for-black-families</t>
   </si>
   <si>
-    <t>2026-10-07T12:58:39.879Z</t>
+    <t>2026-10-08T00:18:11.112Z</t>
   </si>
   <si>
     <t>Jack y Jill y el entrenamiento de la USTA: Tenis para familias negras</t>
@@ -1380,7 +1500,7 @@
     <t>es/home/news/janet-pinkett-building-opportunity-and-joy-in-youth-tennis-thro</t>
   </si>
   <si>
-    <t>2026-10-07T12:58:46.758Z</t>
+    <t>2026-10-08T00:18:16.757Z</t>
   </si>
   <si>
     <t>Janet Pinkett: Construyendo oportunidades y alegría en el tenis juvenil a través del programa Girls Rule the Court ™ de la Fundación USTA Mid-Atlantic.</t>
@@ -1395,7 +1515,7 @@
     <t>es/home/news/jim-loehr-lasting-lessons-for-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T12:58:56.113Z</t>
+    <t>2026-10-08T00:18:23.729Z</t>
   </si>
   <si>
     <t>Las lecciones imperecederas de Jim Loehr para entrenadores de tenis</t>
@@ -1410,7 +1530,7 @@
     <t>es/home/news/john-wilkersons-50-year-coaching-legacy</t>
   </si>
   <si>
-    <t>2026-10-07T12:59:03.063Z</t>
+    <t>2026-10-08T00:18:29.389Z</t>
   </si>
   <si>
     <t>50legado de coaching de John Wilkerson: Lecciones de fe, comunidad y oportunidades</t>
@@ -1425,7 +1545,7 @@
     <t>es/home/news/junior-usa-tennis-shows-true-sportsmanship-at-world-team-cup</t>
   </si>
   <si>
-    <t>2026-10-07T12:59:40.967Z</t>
+    <t>2026-10-08T00:18:35.938Z</t>
   </si>
   <si>
     <t>El equipo juvenil de EE. UU. demuestra verdadera deportividad en la Copa Mundial por Equipos.</t>
@@ -1440,7 +1560,7 @@
     <t>es/home/news/love-serving-autism-coaches-lead-with-acceptance-on-tennis-court</t>
   </si>
   <si>
-    <t>2026-10-07T12:59:48.274Z</t>
+    <t>2026-10-08T00:19:12.098Z</t>
   </si>
   <si>
     <t>Amor al servicio del autismo: Cómo los entrenadores pueden liderar con aceptación en la cancha de tenis.</t>
@@ -1455,7 +1575,7 @@
     <t>es/home/news/make-tennis-more-welcoming-for-everybody</t>
   </si>
   <si>
-    <t>2026-10-07T12:59:54.783Z</t>
+    <t>2026-10-08T00:19:20.004Z</t>
   </si>
   <si>
     <t>Cómo los entrenadores pueden hacer que el tenis sea más accesible para todos.</t>
@@ -1470,7 +1590,7 @@
     <t>es/home/news/michael-harpers-advice-for-tennis-parents-and-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T13:00:01.885Z</t>
+    <t>2026-10-08T00:19:25.989Z</t>
   </si>
   <si>
     <t>Consejos de Michael Harper para padres y entrenadores de tenis: Piensa a largo plazo.</t>
@@ -1485,7 +1605,7 @@
     <t>es/home/news/new-usta-coaching-upgrades</t>
   </si>
   <si>
-    <t>2026-10-07T13:00:09.417Z</t>
+    <t>2026-10-08T00:19:33.071Z</t>
   </si>
   <si>
     <t>Nuevas insignias educativas, aplicación de entrenamiento de la USTA y más.</t>
@@ -1500,7 +1620,7 @@
     <t>es/home/news/paul-annacone-2026-us-open-american-stars-to-watch</t>
   </si>
   <si>
-    <t>2026-10-07T13:00:16.858Z</t>
+    <t>2026-10-08T00:19:40.131Z</t>
   </si>
   <si>
     <t>Paul Annacone 2026 Previa del US Open: Estrellas estadounidenses a seguir</t>
@@ -1515,7 +1635,7 @@
     <t>es/home/news/practical-strategies-and-tips-for-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T13:00:53.179Z</t>
+    <t>2026-10-08T00:19:47.808Z</t>
   </si>
   <si>
     <t>Cómo capacitar el aspecto mental del tenis: estrategias prácticas y consejos para entrenadores de tenis.</t>
@@ -1530,7 +1650,7 @@
     <t>es/home/news/serving-gratitude-celebrating-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:00.194Z</t>
+    <t>2026-10-08T00:19:54.219Z</t>
   </si>
   <si>
     <t>Expresando gratitud: Celebrando a los entrenadores de tenis | USTA Coaching</t>
@@ -1545,7 +1665,7 @@
     <t>es/home/news/southlake-tennis-center-coaching-excellence-world-class-facilities</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:06.957Z</t>
+    <t>2026-10-08T00:20:01.453Z</t>
   </si>
   <si>
     <t>El Southlake Tennis Center fomenta la excelencia en el entrenamiento a través de instalaciones de primer nivel.</t>
@@ -1560,7 +1680,7 @@
     <t>es/home/news/sportimes-playbook-for-the-modern-tennis-coach</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:13.730Z</t>
+    <t>2026-10-08T00:20:08.596Z</t>
   </si>
   <si>
     <t>El manual de Sportime para el entrenador moderno</t>
@@ -1575,7 +1695,7 @@
     <t>es/home/news/sportsmen-tennis-enrichment-center-njtl-leader-boston</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:21.167Z</t>
+    <t>2026-10-08T00:20:15.994Z</t>
   </si>
   <si>
     <t>Centro de Tenis y Enriquecimiento para Deportistas: Un líder de NJTL impulsado por su misión en Boston.</t>
@@ -1590,7 +1710,7 @@
     <t>es/home/news/thomas-judd-coaching-across-continents-ncaa-recruiting-and-business-of-tennis</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:57.078Z</t>
+    <t>2026-10-08T00:20:24.581Z</t>
   </si>
   <si>
     <t>Thomas Judd habla sobre capacitar en diferentes continentes, el reclutamiento en la NCAA y el negocio del tenis.</t>
@@ -1605,7 +1725,7 @@
     <t>es/home/news/usta-ceo-craig-tileys-vision-for-american-tennis</t>
   </si>
   <si>
-    <t>2026-10-07T13:02:04.624Z</t>
+    <t>2026-10-08T00:20:31.330Z</t>
   </si>
   <si>
     <t>La visión del nuevo director ejecutivo de la USTA, Craig Tiley, para el tenis estadounidense | Entrenamiento de la USTA</t>
@@ -1620,7 +1740,7 @@
     <t>es/home/news/usta-coaching-butch-staples-award-2026-coaches-open</t>
   </si>
   <si>
-    <t>2026-10-07T13:02:13.244Z</t>
+    <t>2026-10-08T00:20:39.970Z</t>
   </si>
   <si>
     <t>El premio Butch Staples de la USTA al mejor entrenador se entrega en el Abierto de Entrenadores de 2026</t>
@@ -1635,7 +1755,7 @@
     <t>es/home/news/usta-coaching-collaborates-with-ptm-programs-to-develop-next-generation-tennis-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T13:02:20.239Z</t>
+    <t>2026-10-08T00:21:14.591Z</t>
   </si>
   <si>
     <t>El programa de entrenamiento de la USTA colabora con los programas PTM para desarrollar a la próxima generación de entrenadores de tenis.</t>
@@ -1650,7 +1770,7 @@
     <t>es/home/news/usta-coaching-gives-tennis-coaches-tips-how-to-create-2026-vision-board</t>
   </si>
   <si>
-    <t>2026-10-07T13:02:27.705Z</t>
+    <t>2026-10-08T00:21:49.417Z</t>
   </si>
   <si>
     <t>El servicio de entrenamiento de la USTA ofrece consejos a los entrenadores de tenis sobre cómo crear su tablero de visión 2026</t>
@@ -1665,7 +1785,7 @@
     <t>es/home/news/usta-coaching-launches-inaugural-women-coaching-cohort</t>
   </si>
   <si>
-    <t>2026-10-07T13:02:35.809Z</t>
+    <t>2026-10-08T00:22:25.706Z</t>
   </si>
   <si>
     <t>USTA Coaching lanza su primera cohorte de mujeres en coaching para impulsar el liderazgo</t>
@@ -1680,7 +1800,7 @@
     <t>es/home/news/usta-coaching-online-learning-hub-is-live</t>
   </si>
   <si>
-    <t>2026-10-07T13:03:29.428Z</t>
+    <t>2026-10-19T08:50:50.583Z</t>
   </si>
   <si>
     <t>¡El centro de aprendizaje en línea de entrenamiento de la USTA ya está activo!</t>
@@ -1695,7 +1815,7 @@
     <t>es/home/news/usta-coaching-testimonials-7-coaches-share-their-experience</t>
   </si>
   <si>
-    <t>2026-10-07T13:03:37.181Z</t>
+    <t>2026-10-08T00:23:29.439Z</t>
   </si>
   <si>
     <t>Testimonios de entrenadores de la USTA: 7 Los mejores entrenadores comparten su experiencia</t>
@@ -1710,7 +1830,7 @@
     <t>es/home/news/usta-coaching-wecoach</t>
   </si>
   <si>
-    <t>2026-10-07T13:03:43.311Z</t>
+    <t>2026-10-08T00:23:34.994Z</t>
   </si>
   <si>
     <t>Explora un futuro en el entrenamiento de tenis con USTA Coaching Serving All: Entrenadores aspirantes impulsados por WeCOACH</t>
@@ -1725,7 +1845,7 @@
     <t>es/home/news/usta-dinkins-hbcu-coaching-grant-helped-2-student-athletes-become-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T13:03:51.364Z</t>
+    <t>2026-10-08T00:23:41.865Z</t>
   </si>
   <si>
     <t>Cómo la beca de entrenamiento Dinkins HBCU de la USTA ayudó a dos estudiantes-atletas a convertir en entrenadores</t>
@@ -1740,7 +1860,7 @@
     <t>es/home/news/usta-school-tennis-programs-guide-for-coaches</t>
   </si>
   <si>
-    <t>2026-10-07T13:03:57.768Z</t>
+    <t>2026-10-08T00:23:48.922Z</t>
   </si>
   <si>
     <t>Programas de tenis escolar de la USTA: Guía para entrenadores | Entrenamiento de la USTA</t>
@@ -1755,7 +1875,7 @@
     <t>es/home/news/vania-king-inclusion-culture-pathway-pro</t>
   </si>
   <si>
-    <t>2026-10-07T13:04:05.185Z</t>
+    <t>2026-10-08T00:24:23.199Z</t>
   </si>
   <si>
     <t>Vania King: Lo que los entrenadores de tenis pueden aprender sobre inclusión, cultura y el camino hacia el profesionalismo.</t>
@@ -1770,7 +1890,7 @@
     <t>es/home/news/women-coaches-french-open-immersion-experience</t>
   </si>
   <si>
-    <t>2026-10-07T13:04:12.535Z</t>
+    <t>2026-10-08T00:24:31.637Z</t>
   </si>
   <si>
     <t>Las entrenadoras desarrollan sus habilidades y confianza en una experiencia de inmersión en el Abierto de Francia.</t>
@@ -1785,7 +1905,7 @@
     <t>es/home/news/women-coaches-on-the-mentors-who-shaped-them</t>
   </si>
   <si>
-    <t>2026-10-07T13:04:19.528Z</t>
+    <t>2026-10-08T00:24:38.944Z</t>
   </si>
   <si>
     <t>11 Mujeres coaches hablan sobre los mentores que las formaron y consejos para la próxima generación</t>
@@ -1800,7 +1920,7 @@
     <t>es/home/news/women-in-coaching-advancing-female-tennis-coach-development</t>
   </si>
   <si>
-    <t>2026-10-07T13:04:25.428Z</t>
+    <t>2026-10-08T00:24:44.665Z</t>
   </si>
   <si>
     <t>Mujeres en el entrenamiento: Impulsando el desarrollo de entrenadoras de tenis</t>
@@ -1815,7 +1935,7 @@
     <t>es/home/news/zina-garrison-star-player-to-community-builder</t>
   </si>
   <si>
-    <t>2026-10-07T13:05:01.205Z</t>
+    <t>2026-10-08T00:24:52.262Z</t>
   </si>
   <si>
     <t>Zina Garrison: De jugadora estrella a creadora de comunidad</t>
@@ -2210,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -2320,7 +2440,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -2329,27 +2449,27 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -2361,13 +2481,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -2431,85 +2551,85 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
         <v>39</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
         <v>40</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" t="s">
         <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
         <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -2521,27 +2641,27 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -2553,27 +2673,27 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -2585,27 +2705,27 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -2617,27 +2737,27 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="J13" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -2649,27 +2769,27 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="J14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -2681,27 +2801,27 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="J15" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -2713,27 +2833,27 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="J16" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
@@ -2745,27 +2865,27 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -2777,27 +2897,27 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -2809,27 +2929,27 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I19" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -2841,27 +2961,27 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J20" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -2873,27 +2993,27 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -2905,27 +3025,27 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I22" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="J22" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -2937,27 +3057,27 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I23" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="J23" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2969,27 +3089,27 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
@@ -3001,27 +3121,27 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J25" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
@@ -3033,27 +3153,27 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I26" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="J26" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
@@ -3065,27 +3185,27 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I27" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J27" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
@@ -3097,27 +3217,27 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I28" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="J28" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -3129,27 +3249,27 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I29" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J29" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -3161,27 +3281,27 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I30" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="J30" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -3193,27 +3313,27 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I31" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="J31" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -3225,27 +3345,27 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I32" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="J32" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -3257,27 +3377,27 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I33" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -3289,27 +3409,27 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="J34" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -3321,27 +3441,27 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I35" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J35" t="s">
-        <v>181</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -3353,27 +3473,27 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="I36" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="J36" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
@@ -3385,27 +3505,27 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="I37" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="J37" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -3417,27 +3537,27 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="I38" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="J38" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -3449,27 +3569,27 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="I39" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="J39" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -3481,27 +3601,27 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="I40" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="J40" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
@@ -3513,27 +3633,27 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="I41" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="J41" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
@@ -3545,59 +3665,59 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="I42" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J42" t="s">
-        <v>216</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>219</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="I43" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="J43" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
@@ -3609,27 +3729,27 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="I44" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="J44" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -3641,27 +3761,27 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="I45" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="J45" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -3673,27 +3793,27 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="I46" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="J46" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -3705,27 +3825,27 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="I47" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="J47" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -3737,27 +3857,27 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="I48" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="J48" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -3769,27 +3889,27 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="I49" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="J49" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -3801,27 +3921,27 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="I50" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="J50" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
@@ -3833,27 +3953,27 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="I51" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="J51" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
@@ -3865,59 +3985,59 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="I52" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="J52" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>255</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="E53" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>258</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="I53" t="s">
-        <v>271</v>
+        <v>12</v>
       </c>
       <c r="J53" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -3929,27 +4049,27 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
       </c>
       <c r="G54" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="I54" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="J54" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
@@ -3961,59 +4081,59 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="I55" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J55" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="D56" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>258</v>
       </c>
       <c r="G56" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="I56" t="s">
-        <v>286</v>
+        <v>12</v>
       </c>
       <c r="J56" t="s">
-        <v>287</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -4025,27 +4145,27 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="I57" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="J57" t="s">
-        <v>292</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -4057,27 +4177,27 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="I58" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="J58" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
@@ -4089,27 +4209,27 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="I59" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="J59" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
@@ -4121,27 +4241,27 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="I60" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="J60" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
@@ -4153,27 +4273,27 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="I61" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="J61" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -4185,27 +4305,27 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="I62" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="J62" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
@@ -4217,27 +4337,27 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="I63" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="J63" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
@@ -4249,27 +4369,27 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="I64" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="J64" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
@@ -4281,27 +4401,27 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="I65" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="J65" t="s">
-        <v>332</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
@@ -4313,27 +4433,27 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="I66" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="J66" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
@@ -4345,27 +4465,27 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="I67" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="J67" t="s">
-        <v>342</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
@@ -4377,27 +4497,27 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="I68" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="J68" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -4409,27 +4529,27 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="I69" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="J69" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -4441,27 +4561,27 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="I70" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="J70" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -4473,27 +4593,27 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="I71" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="J71" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -4505,27 +4625,27 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="I72" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="J72" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -4537,27 +4657,27 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="F73" t="s">
         <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="I73" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="J73" t="s">
-        <v>372</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -4569,27 +4689,27 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="F74" t="s">
         <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="I74" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="J74" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
@@ -4601,27 +4721,27 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="I75" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="J75" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
@@ -4633,27 +4753,27 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="I76" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="J76" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
@@ -4665,27 +4785,27 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="F77" t="s">
         <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="I77" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="J77" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
@@ -4697,27 +4817,27 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="I78" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="J78" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -4729,27 +4849,27 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F79" t="s">
         <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="I79" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="J79" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
@@ -4761,27 +4881,27 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="F80" t="s">
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="I80" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="J80" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
@@ -4793,27 +4913,27 @@
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="I81" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="J81" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
@@ -4825,27 +4945,27 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="I82" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="J82" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
@@ -4857,27 +4977,27 @@
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="I83" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="J83" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
@@ -4889,27 +5009,27 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="F84" t="s">
         <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="I84" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="J84" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
@@ -4921,27 +5041,27 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="F85" t="s">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="I85" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="J85" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -4953,27 +5073,27 @@
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="F86" t="s">
         <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="I86" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="J86" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
@@ -4985,27 +5105,27 @@
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="F87" t="s">
         <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="I87" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="J87" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
@@ -5017,27 +5137,27 @@
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="F88" t="s">
         <v>14</v>
       </c>
       <c r="G88" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="I88" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="J88" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
@@ -5049,27 +5169,27 @@
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="F89" t="s">
         <v>14</v>
       </c>
       <c r="G89" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="I89" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="J89" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
@@ -5081,27 +5201,27 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="F90" t="s">
         <v>14</v>
       </c>
       <c r="G90" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="I90" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="J90" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
@@ -5113,27 +5233,27 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="F91" t="s">
         <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H91" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="I91" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="J91" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
@@ -5145,27 +5265,27 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="I92" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="J92" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
@@ -5177,27 +5297,27 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="F93" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="I93" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="J93" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
@@ -5209,27 +5329,27 @@
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="F94" t="s">
         <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="I94" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="J94" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
@@ -5241,27 +5361,27 @@
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="I95" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="J95" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
@@ -5273,27 +5393,27 @@
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="I96" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="J96" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
@@ -5305,27 +5425,27 @@
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="F97" t="s">
         <v>14</v>
       </c>
       <c r="G97" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="I97" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="J97" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
@@ -5337,27 +5457,27 @@
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="F98" t="s">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="I98" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="J98" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
@@ -5369,27 +5489,27 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="F99" t="s">
         <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="I99" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="J99" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
@@ -5401,27 +5521,27 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="I100" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="J100" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
@@ -5433,27 +5553,27 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="F101" t="s">
         <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="I101" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="J101" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
@@ -5465,27 +5585,27 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="F102" t="s">
         <v>14</v>
       </c>
       <c r="G102" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="I102" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="J102" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
@@ -5497,27 +5617,27 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="F103" t="s">
         <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="I103" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="J103" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
@@ -5529,27 +5649,27 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F104" t="s">
         <v>14</v>
       </c>
       <c r="G104" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="I104" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="J104" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
@@ -5561,27 +5681,27 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="F105" t="s">
         <v>14</v>
       </c>
       <c r="G105" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="I105" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="J105" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
@@ -5593,27 +5713,27 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="F106" t="s">
         <v>14</v>
       </c>
       <c r="G106" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="I106" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="J106" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
@@ -5625,27 +5745,27 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="F107" t="s">
         <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="I107" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="J107" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
@@ -5657,27 +5777,27 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="F108" t="s">
         <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H108" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="I108" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="J108" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
@@ -5689,27 +5809,27 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="F109" t="s">
         <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="I109" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="J109" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
@@ -5721,27 +5841,27 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="F110" t="s">
         <v>14</v>
       </c>
       <c r="G110" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="I110" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="J110" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s">
         <v>12</v>
@@ -5753,27 +5873,27 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="F111" t="s">
         <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="I111" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="J111" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="B112" t="s">
         <v>12</v>
@@ -5785,27 +5905,27 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="F112" t="s">
         <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="I112" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="J112" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
@@ -5817,27 +5937,27 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="F113" t="s">
         <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="I113" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="J113" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
@@ -5849,27 +5969,27 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="I114" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="J114" t="s">
-        <v>577</v>
+        <v>560</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="B115" t="s">
         <v>12</v>
@@ -5881,27 +6001,27 @@
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="F115" t="s">
         <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H115" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="I115" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="J115" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
       <c r="B116" t="s">
         <v>12</v>
@@ -5913,27 +6033,27 @@
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="F116" t="s">
         <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="I116" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="J116" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
@@ -5945,27 +6065,27 @@
         <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="F117" t="s">
         <v>14</v>
       </c>
       <c r="G117" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H117" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="I117" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="J117" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="B118" t="s">
         <v>12</v>
@@ -5977,54 +6097,406 @@
         <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="F118" t="s">
         <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="H118" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="I118" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="J118" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>581</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" t="s">
+        <v>582</v>
+      </c>
+      <c r="F119" t="s">
+        <v>14</v>
+      </c>
+      <c r="G119" t="s">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s">
+        <v>583</v>
+      </c>
+      <c r="I119" t="s">
+        <v>584</v>
+      </c>
+      <c r="J119" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>586</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s">
+        <v>587</v>
+      </c>
+      <c r="F120" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>80</v>
+      </c>
+      <c r="H120" t="s">
+        <v>588</v>
+      </c>
+      <c r="I120" t="s">
+        <v>589</v>
+      </c>
+      <c r="J120" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>591</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>592</v>
+      </c>
+      <c r="F121" t="s">
+        <v>14</v>
+      </c>
+      <c r="G121" t="s">
+        <v>80</v>
+      </c>
+      <c r="H121" t="s">
+        <v>593</v>
+      </c>
+      <c r="I121" t="s">
+        <v>594</v>
+      </c>
+      <c r="J121" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>596</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" t="s">
+        <v>597</v>
+      </c>
+      <c r="F122" t="s">
+        <v>14</v>
+      </c>
+      <c r="G122" t="s">
+        <v>80</v>
+      </c>
+      <c r="H122" t="s">
         <v>598</v>
       </c>
-      <c r="B119" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" t="s">
-        <v>12</v>
-      </c>
-      <c r="D119" t="s">
-        <v>12</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="I122" t="s">
         <v>599</v>
       </c>
-      <c r="F119" t="s">
-        <v>14</v>
-      </c>
-      <c r="G119" t="s">
-        <v>39</v>
-      </c>
-      <c r="H119" t="s">
+      <c r="J122" t="s">
         <v>600</v>
       </c>
-      <c r="I119" t="s">
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>601</v>
       </c>
-      <c r="J119" t="s">
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" t="s">
         <v>602</v>
+      </c>
+      <c r="F123" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123" t="s">
+        <v>80</v>
+      </c>
+      <c r="H123" t="s">
+        <v>603</v>
+      </c>
+      <c r="I123" t="s">
+        <v>604</v>
+      </c>
+      <c r="J123" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>606</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" t="s">
+        <v>607</v>
+      </c>
+      <c r="F124" t="s">
+        <v>14</v>
+      </c>
+      <c r="G124" t="s">
+        <v>80</v>
+      </c>
+      <c r="H124" t="s">
+        <v>608</v>
+      </c>
+      <c r="I124" t="s">
+        <v>609</v>
+      </c>
+      <c r="J124" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>611</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" t="s">
+        <v>612</v>
+      </c>
+      <c r="F125" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" t="s">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s">
+        <v>613</v>
+      </c>
+      <c r="I125" t="s">
+        <v>614</v>
+      </c>
+      <c r="J125" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>616</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" t="s">
+        <v>617</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" t="s">
+        <v>80</v>
+      </c>
+      <c r="H126" t="s">
+        <v>618</v>
+      </c>
+      <c r="I126" t="s">
+        <v>619</v>
+      </c>
+      <c r="J126" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>621</v>
+      </c>
+      <c r="B127" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" t="s">
+        <v>622</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" t="s">
+        <v>80</v>
+      </c>
+      <c r="H127" t="s">
+        <v>623</v>
+      </c>
+      <c r="I127" t="s">
+        <v>624</v>
+      </c>
+      <c r="J127" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>626</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>627</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" t="s">
+        <v>80</v>
+      </c>
+      <c r="H128" t="s">
+        <v>628</v>
+      </c>
+      <c r="I128" t="s">
+        <v>629</v>
+      </c>
+      <c r="J128" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>631</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" t="s">
+        <v>632</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
+        <v>80</v>
+      </c>
+      <c r="H129" t="s">
+        <v>633</v>
+      </c>
+      <c r="I129" t="s">
+        <v>634</v>
+      </c>
+      <c r="J129" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>636</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" t="s">
+        <v>637</v>
+      </c>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" t="s">
+        <v>80</v>
+      </c>
+      <c r="H130" t="s">
+        <v>638</v>
+      </c>
+      <c r="I130" t="s">
+        <v>639</v>
+      </c>
+      <c r="J130" t="s">
+        <v>640</v>
       </c>
     </row>
   </sheetData>
